--- a/diabetes_mortality_2021_tidy.xlsx
+++ b/diabetes_mortality_2021_tidy.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5052e625e7f51e50/Desktop/health-data-dashboard/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MSI\OneDrive\Desktop\health-data-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3304E9ED-3F12-4AD5-9B8C-67A47022DF26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFBE5F7B-50A0-4642-9FCC-4EEC7F17547E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1884" yWindow="1884" windowWidth="17280" windowHeight="8880" xr2:uid="{EB1E66E3-3DD9-465E-87F9-A655CCFCC53B}"/>
+    <workbookView xWindow="2340" yWindow="2676" windowWidth="17280" windowHeight="8880" xr2:uid="{EB1E66E3-3DD9-465E-87F9-A655CCFCC53B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>Age group</t>
   </si>
@@ -70,13 +70,22 @@
   </si>
   <si>
     <t>85+</t>
+  </si>
+  <si>
+    <t>Males_rate</t>
+  </si>
+  <si>
+    <t>Females_rate</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,###,###,##0.0"/>
+  </numFmts>
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -84,13 +93,25 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -105,8 +126,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -421,10 +445,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69A5D4C3-29A8-4E68-BE4F-8A4201F23DBC}">
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -434,8 +458,14 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -445,8 +475,14 @@
       <c r="C2">
         <v>216</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D2" s="1">
+        <v>3.8745479889105998</v>
+      </c>
+      <c r="E2" s="1">
+        <v>2.5845989492169399</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -456,8 +492,14 @@
       <c r="C3">
         <v>158</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D3" s="1">
+        <v>31.821817480375501</v>
+      </c>
+      <c r="E3" s="1">
+        <v>18.8144065959975</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -467,8 +509,14 @@
       <c r="C4">
         <v>239</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D4" s="1">
+        <v>61.760874088662703</v>
+      </c>
+      <c r="E4" s="1">
+        <v>30.629716207349102</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -478,8 +526,14 @@
       <c r="C5">
         <v>350</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D5" s="1">
+        <v>92.070878036409397</v>
+      </c>
+      <c r="E5" s="1">
+        <v>45.638224490514403</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -489,8 +543,14 @@
       <c r="C6">
         <v>500</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D6" s="1">
+        <v>166.741588795475</v>
+      </c>
+      <c r="E6" s="1">
+        <v>74.0057694897895</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -500,8 +560,14 @@
       <c r="C7">
         <v>832</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D7" s="1">
+        <v>279.04580124971898</v>
+      </c>
+      <c r="E7" s="1">
+        <v>140.12843984161501</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -511,8 +577,14 @@
       <c r="C8">
         <v>1127</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D8" s="1">
+        <v>485.34413574349401</v>
+      </c>
+      <c r="E8" s="1">
+        <v>248.143328643491</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -522,8 +594,14 @@
       <c r="C9">
         <v>1536</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D9" s="1">
+        <v>862.51277440968795</v>
+      </c>
+      <c r="E9" s="1">
+        <v>503.29797796105402</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -532,6 +610,12 @@
       </c>
       <c r="C10">
         <v>4442</v>
+      </c>
+      <c r="D10" s="1">
+        <v>1826.0672137300201</v>
+      </c>
+      <c r="E10" s="1">
+        <v>1340.5400185297499</v>
       </c>
     </row>
   </sheetData>
